--- a/add-mapping-xds-fhir/ig/submissionSetToPDSM.xlsx
+++ b/add-mapping-xds-fhir/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T09:09:08+00:00</t>
+    <t>2026-09-15T14:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/submissionSetToPDSM.xlsx
+++ b/add-mapping-xds-fhir/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:24:26+00:00</t>
+    <t>2026-09-15T15:11:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/submissionSetToPDSM.xlsx
+++ b/add-mapping-xds-fhir/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:11:37+00:00</t>
+    <t>2026-09-16T10:02:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/submissionSetToPDSM.xlsx
+++ b/add-mapping-xds-fhir/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T10:02:19+00:00</t>
+    <t>2026-09-22T13:51:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/submissionSetToPDSM.xlsx
+++ b/add-mapping-xds-fhir/ig/submissionSetToPDSM.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T13:51:41+00:00</t>
+    <t>2026-09-22T15:20:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-mapping-xds-fhir/ig/submissionSetToPDSM.xlsx
+++ b/add-mapping-xds-fhir/ig/submissionSetToPDSM.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T15:20:18+00:00</t>
+    <t>2026-09-22T17:31:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,9 +123,15 @@
     <t>equivalent</t>
   </si>
   <si>
+    <t>List.identifier:entryUUID</t>
+  </si>
+  <si>
     <t>SubmissionSet.availabilityStatus</t>
   </si>
   <si>
+    <t>related-to</t>
+  </si>
+  <si>
     <t>List.status</t>
   </si>
   <si>
@@ -141,10 +147,16 @@
     <t>List.title</t>
   </si>
   <si>
+    <t>SubmissionSet.comments</t>
+  </si>
+  <si>
+    <t>List.note</t>
+  </si>
+  <si>
     <t>SubmissionSet.patientID</t>
   </si>
   <si>
-    <t>List.subject.fr-core-patient</t>
+    <t>List.subject</t>
   </si>
   <si>
     <t>SubmissionSet.sourceID</t>
@@ -153,6 +165,12 @@
     <t>List.extension:sourceId</t>
   </si>
   <si>
+    <t>SubmissionSet.uniqueID</t>
+  </si>
+  <si>
+    <t>List.identifier:uniqueId</t>
+  </si>
+  <si>
     <t>SubmissionSet.contentTypeCode</t>
   </si>
   <si>
@@ -163,6 +181,12 @@
   </si>
   <si>
     <t>List.source</t>
+  </si>
+  <si>
+    <t>SubmissionSet.intendedRecipient</t>
+  </si>
+  <si>
+    <t>List.extension:intendedRecipient</t>
   </si>
 </sst>
 </file>
@@ -434,7 +458,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -479,99 +503,140 @@
       <c r="C3" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>36</v>
+      </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E13" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
